--- a/Beem Visa Debit - Transformation Phase Project Plan.xlsx
+++ b/Beem Visa Debit - Transformation Phase Project Plan.xlsx
@@ -724,7 +724,7 @@
         <v>46273</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="F11" s="9" t="n">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>46292</v>
+        <v>46275</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46273</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>46273</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
